--- a/data/google_news_dedup_22_0426_UTC_past2d.xlsx
+++ b/data/google_news_dedup_22_0426_UTC_past2d.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -820,22 +820,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nederlandse rapper Knaller veroordeeld voor bezit vuurwapens bij opnames videoclip op Linkeroever - GVA</t>
+          <t>Verdachte gaat vrijuit in zaak rond schietpartij Malpertuisplein Maastricht omdat niet duidelijk is wie geschoten heeft - De Limburger</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Dutch rapper Knaller convicted of possession of firearms during the recording of a video clip on the Left Bank - GVA</t>
+          <t>Suspect goes free in Malpertuisplein Maastricht shooting case because it is not clear who shot - De Limburger</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 10:36:51 GMT</t>
+          <t>Wed, 22 Apr 2026 13:54:45 GMT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxQc0NWYUlnbDlza2c5b29hQndMQnJiNzdKOHZUSDNMX3VfQTR4eUVqNUJQOWIzZzJkUHNPQ2g3T1A0cU5CV3NSLWtPTHdaTFdGbHo4bVhzV296V3dJNmhpMmc3cEV0TElRcU8wVTk5TThMS0lPVGwtTTN3MEx6czJBSW9YNGVmX3I2OUJ3WDFJUld4TVpYNm1QVDBZSjh3Nm05SmN1dDEwQXFQSV9HQWYwcERoV1FuV3ZKZ19xeHJpNUZZdmhfcVBLNkRBdTZWZU1RaF9KQlVSWWN0ZHRaX2hGSE1wZDhPUmc4RzJrbUJ5N0ViWEc0OFhRM01qUFItVVlCaV9n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxNUTlhTk5VMTdEQkVyZWdOblhfUmtCZDhpcXFzMmVuXzJYQkE2aUZTd19jVlZZbHBqSWJiUDJjdHBwdnRXODlWR1ZuVlBRTlBpUl9PRVZsVTBZb3d4TXZRM1RSZkRHSTN0N3U3blVxdFp0WUh3NVU2YzJtaG1rTTZBMTFkZGI5SWllX2xQemJtS0dEaEUxSnhJWmU0cEZSWlJOMDMxUVpLaFVzVnRuVVlUQWVPeU1WeFgxLU9ZZ1NrWDR3N2diSDNqTjFSODVZamRwblc5TXpFenhGaWNmQmNKRlVOai14UkJkZDFNLU1UZ0NkUENSck5qc1B2TFJ5eWQxbXhUUWJxSQ?oc=5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -859,38 +859,38 @@
         </is>
       </c>
       <c r="K8" s="1" t="n">
-        <v>46134.44225694444</v>
+        <v>46134.5796875</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>High Level City Belgium English</t>
+          <t>High Level City Belgium Dutch</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
+          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sardinia targets depopulation with €38 million village tourism push - Travel Tomorrow</t>
+          <t>Dode bij verkeersongeval met vrachtwagen in Venlo - De Limburger</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sardinia targets depopulation with €38 million village tourism push - Travel Tomorrow</t>
+          <t>Death in traffic accident with truck in Venlo - De Limburger</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 08:42:02 GMT</t>
+          <t>Wed, 22 Apr 2026 13:29:23 GMT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQYXczUG1kaUdjc0JUQkNxVlJLRm1yM3d2dE91aGJpQkJKRzJienJ1U2haTUpQMjVRTUs1WkhyRHpwQ1duNzZUbWI5ekJCWmlhdDV1S0JmYlFwaHVWT083b2djS3FIbmVaU05UdHo5OUtKcE5UOElYMThfbGlnd2lhdlZqNm45VlN5NHFSLThmallnYUIwMXlJTk9Ydw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPSXNEV0I2d080YlpiaVYwZTY0bGVGOWZnWEQzdmJQMXM1VFZBaFlESkRFc1ZvWWhSRDNMbDBJZHA1d3dYU2NEOWdkb2pHcDZUWDN1QVB2RUJnVHFPTXhzQlNrdWxwMk0xUzl2OE5ublJVVm1WQm5yOVhWT01IajZkQlBSNV9XOWxEdDBpMUJxZkJGT0g2cWRwbEg1WGNxT0xBZHQ0?oc=5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -910,42 +910,42 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>BE:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K9" s="1" t="n">
-        <v>46134.36252314815</v>
+        <v>46134.56207175926</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>High Level City Belgium English</t>
+          <t>High Level City Belgium Dutch</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
+          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Terror can never be justified: EU expresses solidarity with India on Pahalgam attack anniversary - Social News XYZ</t>
+          <t>‘Woon je in binnenstad, hou dan rekening met inkijk’, stelt de gemeente Maastricht in een rechtszaak over een nieuwbouw - De Limburger</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Terror can never be justified: EU expresses solidarity with India on Pahalgam attack anniversary - Social News XYZ</t>
+          <t>'If you live in the city center, take into account views', says the municipality of Maastricht in a lawsuit about a new building - De Limburger</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 11:33:42 GMT</t>
+          <t>Wed, 22 Apr 2026 13:53:09 GMT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPSWdfUlFDMXdZMy10QlR2SFZfY3JOc1dLWnFMVGI5NjVDXzN5azMzTGwyV0ZDTlFxZXBEZEdEMllzazZvcHYxZWVMZjEwNS1vYnNoa2dPRDE5OWpjS2U5b3hpbDdzNEg1RXFqckZMTXhxVGwwTS1LbVNfa2MzSXl5bnoyR2FZZEdCZnNHOFNPSFNkdVgxX3N1NFdnZlFIRTd4NHY3UVRNdlE2V1A5cUN0M2pHNTdyU2tUbHA5eUp1NmI2RzJBUEw0RTRvQjNBYknSAc8BQVVfeXFMT0lnX1JRQzF3WTMtdEJUdkhWX2NyTnNXS1pxTFRiOTY1Q18zeWszM0xsMldGQ05RcWVwRGRHRDJZc2s2b3B2MWVlTGYxMDUtb2JzaGtnT0QxOTlqY0tlOW94aWw3czRINUVxanJGTE14cVRsME0tS21TX2tjM0l5eW56MkdhWWRHQmZzRzhTT0hTZHVYMV9zdTRXZ2ZRSEU3eDR2N1FUTXZRNldQOXFDdDNqRzU3clNrVGxwOXlKdTZiNkcyQVBMNEU0b0IzQWJJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxOYlMyRnU3TDYybkpBdnFZQ3A0ZWZ1Q0Z0MVdyUjNuMnQzZ1FnMm4wQnMtTXAybDlyeEI4OE50VTU0d0JEUnVaZjFjdmVPTjVRdjdpR19COEFZSFRQZ3NXTVhsajRkWXBnbnc0eXhZUE1XQzVESHdfN01nb1lybklhcXVlRDI3NTNpZWJmdlNUTEZhUE43cXJ3cnNCUUx1QUdYZ09zQ3Rmc193SkIxVmI2ODQ0aUVJRkRVRU5rQ3VFTGpoU2cwUmoxQ0wwLU83N3hBcnNkVUpfTjJ5UktmN0FteHJyVEN4NWFUVGVzNk5yUk4tbXhKNmxTSy00M1dZLUcxQnNqUzZ4MTBXb2I5SGtFbA?oc=5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -965,42 +965,42 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>BE:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K10" s="1" t="n">
-        <v>46134.48173611111</v>
+        <v>46134.57857638889</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>High Level City Belgium English</t>
+          <t>High Level City Belgium Dutch</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
+          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia joins Lithuania-led plan for Brussels memorial to totalitarianism victims - LRT</t>
+          <t>Overbuurman klaagt over weerkaatsend zonlicht op camper in Born en stapt naar de rechter - De Limburger</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Estonia joins Lithuania-led plan for Brussels memorial to totalitarianism victims - LRT</t>
+          <t>Neighbor complains about reflected sunlight on camper in Born and goes to court - De Limburger</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 06:50:00 GMT</t>
+          <t>Wed, 22 Apr 2026 14:09:47 GMT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNQ2J4ZV9vTzkxVDNRcGF6V0JEdjFyMWhFV01KaVdDMHY2TktVNTF1YUhhWE1oX0ZLSFQzNGp3VzROOURpRHRINGNSTEtsdlJfTzkxZzA4TWZfalhLMGRpWHNENnJaZmhaWVc1Ykl0Ny1hQnRDTFB6Z0oweHIwUnl0RnpVVmpuTGoxY29CU1hIU1RldmFGRGRIVGVKTnBTV1pyT19ybjNPVXcyUk1pWlZQS0xjbElyUnhnR2dES19DX0s1blR6a3p5amF3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxNSWJZUThsNGdyTG9UX2JIMUV5U1dISEw2SU03c0lWWVdmX0d5U19zTWlCNGNrRWxqSGpESHk2T2x1dEM3VXpQcVFpbGdfUUFTazF6bXRJOXJRMEVTU2czOTMwVnQxcmtoS1VHcHNRWFdJeG1zaEdhaEk4dDRMRjFXNXRQay1DdHFIVDNiWWg2VFY0ZnoweGhDdkpCRjFNOEl3dUxHZ3ZGNXlleXR5OExwaW5pNS03WmZuUzFsdkkyN25xMi1keWxtYVAzTkd0N05KQmh0a21YS3NLYXNsdmxJNlRFVkIybDNndWc?oc=5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1020,42 +1020,42 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>BE:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K11" s="1" t="n">
-        <v>46134.28472222222</v>
+        <v>46134.59012731481</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>High Level City Belgium English</t>
+          <t>High Level City Belgium Dutch</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
+          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brussels Airlines launches Pan-African Art Tour linking Africa and Europe - Aviation24.be</t>
+          <t>Ravage na brand in Sevenum - De Limburger</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Brussels Airlines launches Pan-African Art Tour linking Africa and Europe - Aviation24.be</t>
+          <t>Devastation after fire in Sevenum - De Limburger</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 10:59:06 GMT</t>
+          <t>Wed, 22 Apr 2026 13:54:39 GMT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTnc0WEUxck9vRlhLQ0ZRYWRiMkJuZER4R0NsTUdDdVEyVmhIUUtKODhQelE2MVQ4cjk1ZFhWbFUya2htR2VNVldSdVp3Z3kwR01ubmRocVB2djlIOTF5dGRxWTIxdmE5RUk0QWhNU3dtbUl2azJrYTl0Tm1UV3E1eWlDTjRXWTJ3eElIeFlfZnMwa0xCWUY1THM3VWdVM3pyUzVuc1V2Wk1FZS1iLVdxM0tEMHV6ZHdCNTFRUmtrbG1OU0hYNlhNakFhLXFYdXJOQnlEeGY0TTZ2M1RGZFUtdtIB4AFBVV95cUxPTnc0WEUxck9vRlhLQ0ZRYWRiMkJuZER4R0NsTUdDdVEyVmhIUUtKODhQelE2MVQ4cjk1ZFhWbFUya2htR2VNVldSdVp3Z3kwR01ubmRocVB2djlIOTF5dGRxWTIxdmE5RUk0QWhNU3dtbUl2azJrYTl0Tm1UV3E1eWlDTjRXWTJ3eElIeFlfZnMwa0xCWUY1THM3VWdVM3pyUzVuc1V2Wk1FZS1iLVdxM0tEMHV6ZHdCNTFRUmtrbG1OU0hYNlhNakFhLXFYdXJOQnlEeGY0TTZ2M1RGZFUtdg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQME5VQjBaRHFXM1NPQ2U3OXVmc05NdFZZSnprX3huQzlOS2hvUkg0N1B4bnJScTZaRjcxSHFLeTUzdDFuc01wVm5tMTJSdWIwY3lSSEZMYzR4bndlNXQ0Z1l5RWo0VXdkVVdIZTNNZ1N3UWFWaXdFcVpJWGhBQk1VNVBYWEE?oc=5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1075,11 +1075,11 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>BE:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K12" s="1" t="n">
-        <v>46134.45770833334</v>
+        <v>46134.57961805556</v>
       </c>
     </row>
     <row r="13">
@@ -1095,22 +1095,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jet fuel prices surge amid W Asia crisis: Lufthansa cuts 20,000 flights, adjusts summer flight schedule - India's News.Net</t>
+          <t>EU unveils plans to tackle energy crisis - Hürriyet Daily News</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Jet fuel prices surge amid W Asia crisis: Lufthansa cuts 20,000 flights, adjusts summer flight schedule - India's News.Net</t>
+          <t>EU unveils plans to tackle energy crisis - Hürriyet Daily News</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 08:10:42 GMT</t>
+          <t>Wed, 22 Apr 2026 08:28:50 GMT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQb2swenhyOWl0eTNzNXE4NEdkNnB1dmlvdXNnMDRJQ3lTVGE3SjUwOGdHTnc2NTh6b1F6WHVxV3N2XzZpeXlhcEF1dV9sT1RwbHlvVWRzUHNDRHlGTjFlX3BxalIyRUVqeTFndklTNmVTMkRfNWhBV3NGejc1cDduRVZjUnBtR2l5T2ljMFBGYU5uUDRSNlFyTGtXR3RYVEZEYlJSZkpBeGxMNG5ieFdJd2puMzBhV3JLMEhKS0Jad3RNMVl0c1kxaVd1S3JSYm5zTHFZUzI2SDlrQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPSVZoLTEzbDdzY0NUVFc1MnRTei1acEJUOV9uNVViMUNleWF1LVhCblpCazZXek5Bc24xQ0VFOVk1THlLRmNrUkh0YTVlekNKUExXV2U2cF9FYVRYXzhBaXAyUXY1QmU1aC1BbkdjTDZlQlBvTXdPZDg4QTNuQk5wd1Z0OEp4WF92ZXdDUE5B?oc=5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1134,38 +1134,38 @@
         </is>
       </c>
       <c r="K13" s="1" t="n">
-        <v>46134.34076388889</v>
+        <v>46134.35335648148</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>High Level City Belgium French</t>
+          <t>High Level City Belgium English</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
+          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Une personne blessée au couteau près du Samusocial - BruxellesToday</t>
+          <t>Sardinia targets depopulation with €38 million village tourism push - Travel Tomorrow</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>A person injured with a knife near Samusocial - BruxellesToday</t>
+          <t>Sardinia targets depopulation with €38 million village tourism push - Travel Tomorrow</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 07:22:30 GMT</t>
+          <t>Wed, 22 Apr 2026 08:42:02 GMT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOSW1WUjBVUUNhV1ZuUzJjV2JPa0xOTVFOclBVUmhjYjJvY293NHZYUFFET0FuZDdTZTR3amlwbDBaMi1XWGZIaXhXcU10bHBuM1hSQVRJODlKcVh2OThGaS1GRmRWWFdDRElsRkhtT2dXNnNpQzVERXVKaHhyN3FuYkhuMG9EM0pmYmg1MlEwZHdISlRB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQYXczUG1kaUdjc0JUQkNxVlJLRm1yM3d2dE91aGJpQkJKRzJienJ1U2haTUpQMjVRTUs1WkhyRHpwQ1duNzZUbWI5ekJCWmlhdDV1S0JmYlFwaHVWT083b2djS3FIbmVaU05UdHo5OUtKcE5UOElYMThfbGlnd2lhdlZqNm45VlN5NHFSLThmallnYUIwMXlJTk9Ydw?oc=5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1185,42 +1185,42 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>BE:en</t>
         </is>
       </c>
       <c r="K14" s="1" t="n">
-        <v>46134.30729166666</v>
+        <v>46134.36252314815</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>High Level City Belgium French</t>
+          <t>High Level City Belgium English</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
+          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Le parquet réclame 15 mois de détention pour une "agression antisémite" commise à l'ULB - BruxellesToday</t>
+          <t>Terror can never be justified: EU expresses solidarity with India on Pahalgam attack anniversary - Social News XYZ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>The prosecution demands 15 months of detention for an “anti-Semitic attack” committed at the ULB - BruxellesToday</t>
+          <t>Terror can never be justified: EU expresses solidarity with India on Pahalgam attack anniversary - Social News XYZ</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 07:01:00 GMT</t>
+          <t>Wed, 22 Apr 2026 11:33:42 GMT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOcFhYU1NTWnl1UHR6dHY5cFFmc21XbF90UnJzOTBiLTE4bEtMRnoyRUgtMmZsVURrYklLS19rTlM4b0xLZTk4QXJYNjBNbU5OQU1UTF9rb3MzMzFMbW5JbVJiZW9QdlR6ZFVoN3NISDZKQUZIelJxQTNpd2tfNzAycDhCRkxMVUtyV2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPSWdfUlFDMXdZMy10QlR2SFZfY3JOc1dLWnFMVGI5NjVDXzN5azMzTGwyV0ZDTlFxZXBEZEdEMllzazZvcHYxZWVMZjEwNS1vYnNoa2dPRDE5OWpjS2U5b3hpbDdzNEg1RXFqckZMTXhxVGwwTS1LbVNfa2MzSXl5bnoyR2FZZEdCZnNHOFNPSFNkdVgxX3N1NFdnZlFIRTd4NHY3UVRNdlE2V1A5cUN0M2pHNTdyU2tUbHA5eUp1NmI2RzJBUEw0RTRvQjNBYknSAc8BQVVfeXFMT0lnX1JRQzF3WTMtdEJUdkhWX2NyTnNXS1pxTFRiOTY1Q18zeWszM0xsMldGQ05RcWVwRGRHRDJZc2s2b3B2MWVlTGYxMDUtb2JzaGtnT0QxOTlqY0tlOW94aWw3czRINUVxanJGTE14cVRsME0tS21TX2tjM0l5eW56MkdhWWRHQmZzRzhTT0hTZHVYMV9zdTRXZ2ZRSEU3eDR2N1FUTXZRNldQOXFDdDNqRzU3clNrVGxwOXlKdTZiNkcyQVBMNEU0b0IzQWJJ?oc=5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1240,42 +1240,42 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>BE:en</t>
         </is>
       </c>
       <c r="K15" s="1" t="n">
-        <v>46134.29236111111</v>
+        <v>46134.48173611111</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>High Level City Belgium French</t>
+          <t>High Level City Belgium English</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
+          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Accusations de violences sexuelles: une pétition demande l'annulation de la tournée de Patrick Bruel - Boursorama</t>
+          <t>Brussels Airlines launches Pan-African Art Tour linking Africa and Europe - Aviation24.be</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Accusations of sexual violence: a petition calls for the cancellation of Patrick Bruel's tour - Boursorama</t>
+          <t>Brussels Airlines launches Pan-African Art Tour linking Africa and Europe - Aviation24.be</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 06:48:36 GMT</t>
+          <t>Wed, 22 Apr 2026 10:59:06 GMT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAJBVV95cUxNcG40VlNDU2wyLXIwdXFoSF9tX09fREJHM3V3eVg5SUJDbFh2bnRFSU94Z2llWFRydHo4VjdNTU1kSUc0ZEM1TGRnYWhUMUFhbDJ5Ql9wSXRfMzhUR056TThSVzM1VU5kUE9PQnl5dWthYnpUSlltd05UVXRwNzZDMWVhODRfSHZXSTc3OXU4QU5RcU5ZdUFVQm9jY1dJRFQ3YkE2cjItQTlXUHFCWXNCY25JdVAyOWZUWERrWTJoYl8wNGlsQlJHVVBYTVRzY3lvV3E5bGVBWjh1OGxDUWhnaGtfcGhnelJ4NTM0SkJYR0hBd2RydHJTazdTbHdnV2pWME83akM5MGNSdEJDSEdwRVZFUEtEeHNOYjlTZ3FGWUvSAaACQVVfeXFMTXBuNFZTQ1NsMi1yMHVxaEhfbV9PX0RCRzN1d3lYOUlCQ2xYdm50RUlPeGdpZVhUcnR6OFY3TU1NZElHNGRDNUxkZ2FoVDFBYWwyeUJfcEl0XzM4VEdOek04UlczNVVOZFBPT0J5eXVrYWJ6VEpZbXdOVFV0cDc2QzFlYTg0X0h2V0k3Nzl1OEFOUXFOWXVBVUJvY2NXSURUN2JBNnIyLUE5V1BxQllzQmNuSXVQMjlmVFhEa1kyaGJfMDRpbEJSR1VQWE1Uc2N5b1dxOWxlQVo4dThsQ1FoZ2hrX3BoZ3pSeDUzNEpCWEdIQXdkcnRyU2s3U2x3Z1dqVjBPN2pDOTBjUnRCQ0hHcEVWRVBLRHhzTmI5U2dxRllL?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTnc0WEUxck9vRlhLQ0ZRYWRiMkJuZER4R0NsTUdDdVEyVmhIUUtKODhQelE2MVQ4cjk1ZFhWbFUya2htR2VNVldSdVp3Z3kwR01ubmRocVB2djlIOTF5dGRxWTIxdmE5RUk0QWhNU3dtbUl2azJrYTl0Tm1UV3E1eWlDTjRXWTJ3eElIeFlfZnMwa0xCWUY1THM3VWdVM3pyUzVuc1V2Wk1FZS1iLVdxM0tEMHV6ZHdCNTFRUmtrbG1OU0hYNlhNakFhLXFYdXJOQnlEeGY0TTZ2M1RGZFUtdtIB4AFBVV95cUxPTnc0WEUxck9vRlhLQ0ZRYWRiMkJuZER4R0NsTUdDdVEyVmhIUUtKODhQelE2MVQ4cjk1ZFhWbFUya2htR2VNVldSdVp3Z3kwR01ubmRocVB2djlIOTF5dGRxWTIxdmE5RUk0QWhNU3dtbUl2azJrYTl0Tm1UV3E1eWlDTjRXWTJ3eElIeFlfZnMwa0xCWUY1THM3VWdVM3pyUzVuc1V2Wk1FZS1iLVdxM0tEMHV6ZHdCNTFRUmtrbG1OU0hYNlhNakFhLXFYdXJOQnlEeGY0TTZ2M1RGZFUtdg?oc=5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1295,42 +1295,42 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>BE:en</t>
         </is>
       </c>
       <c r="K16" s="1" t="n">
-        <v>46134.28375</v>
+        <v>46134.45770833334</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>High Level City Belgium French</t>
+          <t>High Level City Belgium English</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
+          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Malaise du chauffeur: le bus scolaire quitte la route et s'écrase contre un arbre - BruxellesToday</t>
+          <t>Jet fuel prices surge amid W Asia crisis: Lufthansa cuts 20,000 flights, adjusts summer flight schedule - India's News.Net</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Driver's discomfort: school bus leaves the road and crashes into a tree - BruxellesToday</t>
+          <t>Jet fuel prices surge amid W Asia crisis: Lufthansa cuts 20,000 flights, adjusts summer flight schedule - India's News.Net</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 08:12:59 GMT</t>
+          <t>Wed, 22 Apr 2026 13:31:00 GMT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOYmVzTXI0OHpaYXlEa0xEanRKNUpDRmFubE94ZGdhc1dlb3dwcDFOa0RUTXRob1lQclk4ajAxajI0R3F4LVkzemV6VVIwNVp4UVFCaml0eXJaS19YME15c1FNUFFRZ3FpR0JMVWl2MHplSEplV0VXeFdBVl9iQ0t3Zg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQb2swenhyOWl0eTNzNXE4NEdkNnB1dmlvdXNnMDRJQ3lTVGE3SjUwOGdHTnc2NTh6b1F6WHVxV3N2XzZpeXlhcEF1dV9sT1RwbHlvVWRzUHNDRHlGTjFlX3BxalIyRUVqeTFndklTNmVTMkRfNWhBV3NGejc1cDduRVZjUnBtR2l5T2ljMFBGYU5uUDRSNlFyTGtXR3RYVEZEYlJSZkpBeGxMNG5ieFdJd2puMzBhV3JLMEhKS0Jad3RNMVl0c1kxaVd1S3JSYm5zTHFZUzI2SDlrQQ?oc=5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1350,11 +1350,11 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>BE:en</t>
         </is>
       </c>
       <c r="K17" s="1" t="n">
-        <v>46134.34234953704</v>
+        <v>46134.56319444445</v>
       </c>
     </row>
     <row r="18">
@@ -1370,22 +1370,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Prix de l’énergie : Bruxelles sort l’arsenal d’urgence face au choc du Moyen-Orient - Revue Passages</t>
+          <t>Une personne blessée au couteau près du Samusocial - BruxellesToday</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Energy prices: Brussels draws out emergency arsenal in the face of the Middle East shock - Revue Passages</t>
+          <t>A person injured with a knife near Samusocial - BruxellesToday</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 12:50:44 GMT</t>
+          <t>Wed, 22 Apr 2026 07:22:30 GMT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPeUJXeFUxanpWV2ZTMHotOUhZU0VvWDRJNEhsaXdpcFltd0dYV1ZaZjE0Yk80ZjlFOFVJTzg4U19OZnp2NWxybkE4bGlPeWhxSGhXam1BWnZBZmhNSW9Odmp0NmVJMUJGcF9QODd4UFRnRzJ3ZlIwRmZsRFljYWVzZnVZem55eU9xSmxTeWR6R3Zjcm4yVGtCQVRDQVdxNGE1V0lMd0ZjVGhfT2VTWGk4ME9aMHlJalU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOSW1WUjBVUUNhV1ZuUzJjV2JPa0xOTVFOclBVUmhjYjJvY293NHZYUFFET0FuZDdTZTR3amlwbDBaMi1XWGZIaXhXcU10bHBuM1hSQVRJODlKcVh2OThGaS1GRmRWWFdDRElsRkhtT2dXNnNpQzVERXVKaHhyN3FuYkhuMG9EM0pmYmg1MlEwZHdISlRB?oc=5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1409,38 +1409,38 @@
         </is>
       </c>
       <c r="K18" s="1" t="n">
-        <v>46134.53523148148</v>
+        <v>46134.30729166666</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen French (fallback)</t>
+          <t>High Level City Belgium French</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
+          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>« Comment la justice pourrait statuer sereinement alors qu’il se produit sur toutes les scènes ? » : une pétition réclame l’annulation de la tournée de Patrick Bruel - RTL Info</t>
+          <t>Malaise du chauffeur: le bus scolaire quitte la route et s'écrase contre un arbre - BruxellesToday</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>“How could justice rule calmly when he performs on all stages? »: a petition calls for the cancellation of Patrick Bruel's tour - RTL Info</t>
+          <t>Driver's discomfort: school bus leaves the road and crashes into a tree - BruxellesToday</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 09:12:06 GMT</t>
+          <t>Wed, 22 Apr 2026 08:12:59 GMT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOb2hmNEhrM21MVmJzVEtyRlBXbGNQbGlOajgxX2t4TThjazZqZEl0MlVkLVVSaHdjUkZQU3hWbmJSc05zN05YUEI0WDdxYWpobE8wUWtEOWhZMUdTYl83b0xCcDRfVlFxd09VNE42T0ZKY3RQNkxyQWdMb0R2SXlOQWFrd2ZOUkdQRmU2aVpxc0RsTEZZU3pwTUZwMXpyZXNYWGxaTDVzN1BnVjlmYlJxbURQUmRYZUNlUDhLNUY2WVpiYzRNal9TSEg4RnQ2U1ZJWG5z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOYmVzTXI0OHpaYXlEa0xEanRKNUpDRmFubE94ZGdhc1dlb3dwcDFOa0RUTXRob1lQclk4ajAxajI0R3F4LVkzemV6VVIwNVp4UVFCaml0eXJaS19YME15c1FNUFFRZ3FpR0JMVWl2MHplSEplV0VXeFdBVl9iQ0t3Zg?oc=5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1464,38 +1464,38 @@
         </is>
       </c>
       <c r="K19" s="1" t="n">
-        <v>46134.38340277778</v>
+        <v>46134.34234953704</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen French (fallback)</t>
+          <t>High Level City Belgium French</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
+          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Un bus scolaire percute un arbre en Flandre: cinq blessés - 7sur7.be</t>
+          <t>Prix de l’énergie : Bruxelles sort l’arsenal d’urgence face au choc du Moyen-Orient - Revue Passages</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>A school bus hits a tree in Flanders: five injured - 7sur7.be</t>
+          <t>Energy prices: Brussels draws out emergency arsenal in the face of the Middle East shock - Revue Passages</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 07:10:00 GMT</t>
+          <t>Wed, 22 Apr 2026 12:50:44 GMT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOWHZrYVBfQzZnaEk0VEk5RmctV1JXWFBJTXBuaHp2Z0NvYmN5aVZsNGpYQ3pySjloVlVlUVNIQmpDbG5HaGpiYzAwMXVuck5Hd0p2eFBkaUd3X09meURsZHQ1VU01QkowV2x3LUNRVkVnY3NVN3lZZ2F5VFFlWG9LZTRiSnkyVmtfSE1MRWtuWHVXcno2aWtabXdUZEx5ejZRamc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPeUJXeFUxanpWV2ZTMHotOUhZU0VvWDRJNEhsaXdpcFltd0dYV1ZaZjE0Yk80ZjlFOFVJTzg4U19OZnp2NWxybkE4bGlPeWhxSGhXam1BWnZBZmhNSW9Odmp0NmVJMUJGcF9QODd4UFRnRzJ3ZlIwRmZsRFljYWVzZnVZem55eU9xSmxTeWR6R3Zjcm4yVGtCQVRDQVdxNGE1V0lMd0ZjVGhfT2VTWGk4ME9aMHlJalU?oc=5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="K20" s="1" t="n">
-        <v>46134.29861111111</v>
+        <v>46134.53523148148</v>
       </c>
     </row>
     <row r="21">
@@ -1535,22 +1535,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kamel Daoud annonce avoir écopé de trois ans de prison en Algérie pour «Houris» - Le Devoir</t>
+          <t>« Comment la justice pourrait statuer sereinement alors qu’il se produit sur toutes les scènes ? » : une pétition réclame l’annulation de la tournée de Patrick Bruel - RTL Info</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Kamel Daoud announces having received three years in prison in Algeria for “Houris” - Le Devoir</t>
+          <t>“How could justice rule calmly when he performs on all stages? »: a petition calls for the cancellation of Patrick Bruel's tour - RTL Info</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 12:52:20 GMT</t>
+          <t>Wed, 22 Apr 2026 09:12:06 GMT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPUDFzc1RYRVFMTDB1S3VWWVU1WC1VZGRGaEtWSW9DUl9RT3dOYkd2RlVaZ0JrTndEN2FvMVNNcjBlcVFFN3pzMzZtQ2hLVFpjNmd2VzhsbDR2MEdJNmI2YjU5LVZjc1pGZHp3c3p6bEtNOEhVTnlKYkFNRE5rT1c1dlF2OWI0Q0h3MUYyRFdTQTZYY3lERVpnbjctSWlkVVpIb3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOb2hmNEhrM21MVmJzVEtyRlBXbGNQbGlOajgxX2t4TThjazZqZEl0MlVkLVVSaHdjUkZQU3hWbmJSc05zN05YUEI0WDdxYWpobE8wUWtEOWhZMUdTYl83b0xCcDRfVlFxd09VNE42T0ZKY3RQNkxyQWdMb0R2SXlOQWFrd2ZOUkdQRmU2aVpxc0RsTEZZU3pwTUZwMXpyZXNYWGxaTDVzN1BnVjlmYlJxbURQUmRYZUNlUDhLNUY2WVpiYzRNal9TSEg4RnQ2U1ZJWG5z?oc=5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="K21" s="1" t="n">
-        <v>46134.53634259259</v>
+        <v>46134.38340277778</v>
       </c>
     </row>
     <row r="22">
@@ -1590,22 +1590,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pronostic : Patro Eisden Maasmechelen vs K. Beerschot V.A. | 23/04/2026 - Footix.fr</t>
+          <t>Cet animal aperçu le long d'un canal belge fait le buzz: "Les gens en ont presque fait un passe-temps " - La Libre.be</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Pronostic: Patro Eisden Maasmechelen vs K. Beerschot V.A. | 23/04/2026 - Footix.fr</t>
+          <t>This animal seen along a Belgian canal is causing a buzz: “People have almost made it a hobby” - La Libre.be</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 10:31:59 GMT</t>
+          <t>Wed, 22 Apr 2026 10:43:00 GMT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQQzNRd3VBOE9jTDQ4SVVwSGJnU2NVb056QUpzNDBfdl9pNXU4M3NhYmtkYmY4UGJYcVNxNGFZSXh0TEZjTnM4SUU2RHhhMWlLazFDN3BSb19YVW1HM0oyUFZKLU5vVHZWZVRqRGZiRnJobjFpbXgzYjBlZ0syOXRWcWhNTUpUWkJuOGs5WlZhbWNjZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxPQVViT3dZYTF5ZDRYYU1NQlAtMm5ham1HQnBEOEdCTHBrZHFWdm55V3ZhSE5mdHVmZlprcTYzWmFfRjZfV1hLU0JTYWx2bkdVSEdiTXhPSGVOSm95M0F3STBZZlUyNXU1Mi0xWDczWkRuRUxqVWwwR1l4VUtoNHNQY01FLXRqajh0MWNyd1UtdWE1X2FHMlBaazlOS3N2V2ozTG5ZVUFxV2xSMklGZ0FqelpxSzZ4VGhOSVp0TDdTdXdIQWZ5Sm9vZnZoMEpmelNsTG1vR25uc1BfbEt2NXZxb3BFaDYyaDhhaTBxZ0w1UUtKbTNiZ3lpU1F0UXhEV2thSk55Qmdsdw?oc=5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1629,13 +1629,13 @@
         </is>
       </c>
       <c r="K22" s="1" t="n">
-        <v>46134.43887731482</v>
+        <v>46134.44652777778</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen English (fallback)</t>
+          <t>Local Town Maasmechelen French (fallback)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1645,22 +1645,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Uber takes stake in French hydrogen taxi start-up - The Local France</t>
+          <t>Année de célébrations pour les 200 ans de South Willemsvaart - fr.flows.be</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Uber takes stake in French hydrogen taxi start-up - The Local France</t>
+          <t>Year of celebrations for 200 years of South Willemsvaart - fr.flows.be</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 11:22:40 GMT</t>
+          <t>Wed, 22 Apr 2026 10:03:00 GMT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNaXZTWmJyeVZ4STZlU0EzbzdKbUM4VE1yRzNVbGFJUU0ydDBybFlEd2JwVTY0WVBRMjRrbVFqdnhmRWs1dXAzSzVtX3BTci0wU2tXMm13bm5kZjluWmNkY0tjQ1JVZmpLRWZxSW5rRG0tZ2E0WTF2aDJJS1ZtU2NPWHVoWExWdlc2enc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxORUZ6ZnJsQmtrckJDM0JXX1hSdnM0akRBQk5jdXFick43YWMxQVQ0TFk3VWdoYXJaRXpLQlZ6X2prZE1RdFB1Y293Y29WOFYwQ2V6akY2dTR5WWltZ1E0dnRwNVdBdlpSaFBpeHFqVWNuZWpCT08yMlZqdkpmdnoxZGRWeUZETEo0a21SZzRIQzZpSXByQ0dvXzJtSV9zVlJTM2tNVzEtbGNIcVp2QVZSXw?oc=5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1670,52 +1670,52 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:fr</t>
         </is>
       </c>
       <c r="K23" s="1" t="n">
-        <v>46134.47407407407</v>
+        <v>46134.41875</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Local Town Wertheim German</t>
+          <t>Local Town Maasmechelen French (fallback)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>( "Wertheim" OR "Wurzburg" OR "Aschaffenburg") AND ("protest" OR "protestieren" OR "boykottieren" OR "Boykott" OR "Bombe" OR "Bombendrohung" OR "verdächtiges Paket" OR "unbeaufsichtigtes Paket" OR "explosion"  OR "Sprengstoffe" OR "Schießen" OR "Stechend" OR "Messerstecherei")</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lehrkräfte und GEW protestieren gegen Zulassungsstopp bei Integrationskursen - aschaffenburg.news</t>
+          <t>Kamel Daoud annonce avoir écopé de trois ans de prison en Algérie pour «Houris» - Le Devoir</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Teachers and GEW protest against the ban on admission to integration courses - aschaffenburg.news</t>
+          <t>Kamel Daoud announces having received three years in prison in Algeria for “Houris” - Le Devoir</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 11:48:29 GMT</t>
+          <t>Wed, 22 Apr 2026 12:52:20 GMT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQTklaWTNWVUxTWWptWGk3SUpNZ2lWRElpQnp3SXVvTDBFWDlVZ1dZelp4ZnI5WnJmQy1hQjlWcHFlejMybm5hWlRqWFhYam1CZXNrRFJoUzlrMEhSaWxzdGNwVEtxU1d5d24waW41WXlZOHNlRE5lYWk2OVhnVk9zNjJEWndjWGoyRU4xS0MtaGlDVERFTVJqZ3RfSGN0TXQzTzRCM1pFLTJNaWh1ZWdoU09GcjNzSTF5OW5rQ0Z4X2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPUDFzc1RYRVFMTDB1S3VWWVU1WC1VZGRGaEtWSW9DUl9RT3dOYkd2RlVaZ0JrTndEN2FvMVNNcjBlcVFFN3pzMzZtQ2hLVFpjNmd2VzhsbDR2MEdJNmI2YjU5LVZjc1pGZHp3c3p6bEtNOEhVTnlKYkFNRE5rT1c1dlF2OWI0Q0h3MUYyRFdTQTZYY3lERVpnbjctSWlkVVpIb3c?oc=5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1725,52 +1725,52 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>DE:de</t>
+          <t>BE:fr</t>
         </is>
       </c>
       <c r="K24" s="1" t="n">
-        <v>46134.49200231482</v>
+        <v>46134.53634259259</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Village Wertheim (fallback)</t>
+          <t>Local Town Maasmechelen French (fallback)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Why Elena Rybakina’s consistency is changing WTA race - Newswav</t>
+          <t>Pronostic : Patro Eisden Maasmechelen vs K. Beerschot V.A. | 23/04/2026 - Footix.fr</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Why Elena Rybakina’s consistency is changing WTA race - Newswav</t>
+          <t>Pronostic : Patro Eisden Maasmechelen vs K. Beerschot V.A. | 23/04/2026 - Footix.fr</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 12:49:11 GMT</t>
+          <t>Wed, 22 Apr 2026 10:31:59 GMT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOYVRmLXJRVDQ2WjlpVURUSGVtbEVaRVZYaVEyX1c3YUtGaHJtZUVzNjUzbl95VTVQR0dPVDd5cUlFcGlKLXl2WXNxRTd1WVpiRGltdjYwbk1mb2gycE5KbW95SzB3Mm1XLUhQQklYRGxub3FPUnBzLVoxd1JOQ3RJVzRPNFFicGkxUzFCaEpjdm8ybEFEMkNsM21B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQQzNRd3VBOE9jTDQ4SVVwSGJnU2NVb056QUpzNDBfdl9pNXU4M3NhYmtkYmY4UGJYcVNxNGFZSXh0TEZjTnM4SUU2RHhhMWlLazFDN3BSb19YVW1HM0oyUFZKLU5vVHZWZVRqRGZiRnJobjFpbXgzYjBlZ0syOXRWcWhNTUpUWkJuOGs5WlZhbWNjZw?oc=5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1780,52 +1780,52 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:fr</t>
         </is>
       </c>
       <c r="K25" s="1" t="n">
-        <v>46134.5341550926</v>
+        <v>46134.43887731482</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Local Town Ingolstadt German</t>
+          <t>Local Town Wertheim German</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>("Ingolstadt") AND (Protest OR Bombe OR Bombendrohung OR Explosion OR Schießerei OR Polizei OR Evakuierung OR Terrorverdacht) AND -Audi AND -Auto AND -Wetter</t>
+          <t>( "Wertheim" OR "Wurzburg" OR "Aschaffenburg") AND ("protest" OR "protestieren" OR "boykottieren" OR "Boykott" OR "Bombe" OR "Bombendrohung" OR "verdächtiges Paket" OR "unbeaufsichtigtes Paket" OR "explosion"  OR "Sprengstoffe" OR "Schießen" OR "Stechend" OR "Messerstecherei")</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Polizei stoppt Autofahrer mit 1,5 Promille und ohne Führerschein - Augsburger Allgemeine</t>
+          <t>Lehrkräfte und GEW protestieren gegen Zulassungsstopp bei Integrationskursen - aschaffenburg.news</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Police stop drivers with 1.5 per mille and without a driver's license - Augsburger Allgemeine</t>
+          <t>Teachers and GEW protest against the ban on admission to integration courses - aschaffenburg.news</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 10:25:25 GMT</t>
+          <t>Wed, 22 Apr 2026 11:48:29 GMT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQY1JkTVRGZGJHT2tOTTRHTEZ0Q2dRckN2TWFFTERrV1pPT1lZYzZIczRWY2wzdnpUZ0g4OHE4cWdMVXlJTTdZZXdURUFKb0NKMUFCaGpPM2ZTMTM1UGRmSENWTlpLVlhMcnlPUmxBMVFSXy1mWFhTb1RrbmNYRDh5LWp1ZzJzVmUwYmhwMGRkSWR0akgwR0xRVXJkc2JoVEhzWXBNclUxRlh6MHRVR2YwTUVLclVBcnY2WC1UTHVaWk42bzk5Ymc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQTklaWTNWVUxTWWptWGk3SUpNZ2lWRElpQnp3SXVvTDBFWDlVZ1dZelp4ZnI5WnJmQy1hQjlWcHFlejMybm5hWlRqWFhYam1CZXNrRFJoUzlrMEhSaWxzdGNwVEtxU1d5d24waW41WXlZOHNlRE5lYWk2OVhnVk9zNjJEWndjWGoyRU4xS0MtaGlDVERFTVJqZ3RfSGN0TXQzTzRCM1pFLTJNaWh1ZWdoU09GcjNzSTF5OW5rQ0Z4X2c?oc=5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1849,38 +1849,38 @@
         </is>
       </c>
       <c r="K26" s="1" t="n">
-        <v>46134.43431712963</v>
+        <v>46134.49200231482</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Village Ingolstadt (fallback)</t>
+          <t>Village Wertheim (fallback)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>("Ingolstadt Village" OR "Ingolstadt") AND (shopping OR outlet OR luxury OR retail OR news)</t>
+          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ingolstadt, Bavaria Weather Forecast | MSN Weather - MSN</t>
+          <t>Why Elena Rybakina’s consistency is changing WTA race - Newswav</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Ingolstadt, Bavaria Weather Forecast | MSN Weather - MSN</t>
+          <t>Why Elena Rybakina’s consistency is changing WTA race - Newswav</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 07:42:46 GMT</t>
+          <t>Wed, 22 Apr 2026 12:49:11 GMT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOcnhQOThXU3hIaWsxVHdVdGdFdjA4eHVLODhoR3pVdTVUY0Z3MEhfYzBjWVNtbHFkLXB5M3FvR0dqclV3d2FCZzJVOHg3UmtNejBBS2ZhTllTaWlES09IRHdheUtVU0NjYWRZS19qV1V6SGVWbHhmUjRxd0hyOWR3OXh4a0lpamxaNlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOYVRmLXJRVDQ2WjlpVURUSGVtbEVaRVZYaVEyX1c3YUtGaHJtZUVzNjUzbl95VTVQR0dPVDd5cUlFcGlKLXl2WXNxRTd1WVpiRGltdjYwbk1mb2gycE5KbW95SzB3Mm1XLUhQQklYRGxub3FPUnBzLVoxd1JOQ3RJVzRPNFFicGkxUzFCaEpjdm8ybEFEMkNsM21B?oc=5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1904,38 +1904,38 @@
         </is>
       </c>
       <c r="K27" s="1" t="n">
-        <v>46134.32136574074</v>
+        <v>46134.5341550926</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>High Level City UK Ireland</t>
+          <t>Local Town Ingolstadt German</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
+          <t>("Ingolstadt") AND (Protest OR Bombe OR Bombendrohung OR Explosion OR Schießerei OR Polizei OR Evakuierung OR Terrorverdacht) AND -Audi AND -Auto AND -Wetter</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026 film and high-end TV productions shooting in the UK and Ireland: latest updates - Screen Daily</t>
+          <t>Polizei stoppt Autofahrer mit 1,5 Promille und ohne Führerschein - Augsburger Allgemeine</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026 film and high-end TV productions shooting in the UK and Ireland: latest updates - Screen Daily</t>
+          <t>Police stop drivers with 1.5 per mille and without a driver's license - Augsburger Allgemeine</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 11:48:08 GMT</t>
+          <t>Wed, 22 Apr 2026 10:25:25 GMT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQZmNMRTBhWHdsbFo0WHUtenBKUWJ0Z09LVVBuTjVUb1R6dnYyV0UwSEluX01NUXJuVzhuVlZCTUlHanpOQ0hpT1p4N2xGSnIyaEg3eGRKQ3BZVlJWT0hPREU4dmd2azc2VGVhQVl2emFKVmpENnNrT3BJNGVDY2xlNDVSUV95dzdPcHFtOHhqcG9WbUdYYU9odjhUTHp2b0dzMTZ6Yzh4U1VGNVVfeVl5RmQ1eDJpLU91MHlMUS1kZlZNNng3LTE1VHNIb1o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQY1JkTVRGZGJHT2tOTTRHTEZ0Q2dRckN2TWFFTERrV1pPT1lZYzZIczRWY2wzdnpUZ0g4OHE4cWdMVXlJTTdZZXdURUFKb0NKMUFCaGpPM2ZTMTM1UGRmSENWTlpLVlhMcnlPUmxBMVFSXy1mWFhTb1RrbmNYRDh5LWp1ZzJzVmUwYmhwMGRkSWR0akgwR0xRVXJkc2JoVEhzWXBNclUxRlh6MHRVR2YwTUVLclVBcnY2WC1UTHVaWk42bzk5Ymc?oc=5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1945,52 +1945,52 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>de</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>DE:de</t>
         </is>
       </c>
       <c r="K28" s="1" t="n">
-        <v>46134.49175925926</v>
+        <v>46134.43431712963</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>High Level City UK Ireland</t>
+          <t>Village Ingolstadt (fallback)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
+          <t>("Ingolstadt Village" OR "Ingolstadt") AND (shopping OR outlet OR luxury OR retail OR news)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Terrorist who planned to bomb London Stock Exchange was allowed to stay in UK - The Sun</t>
+          <t>Ingolstadt, Bavaria Weather Forecast | MSN Weather - MSN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Terrorist who planned to bomb London Stock Exchange was allowed to stay in UK - The Sun</t>
+          <t>Ingolstadt, Bavaria Weather Forecast | MSN Weather - MSN</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 08:10:00 GMT</t>
+          <t>Wed, 22 Apr 2026 07:42:46 GMT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOZFlwT3NoaG5aZXY3a25VYlJIWGZ6VERlRVNZZHF4dmVLaEtQLXJLTVJtRF9ydHhSOVhEWlozeXUycWIyeHkwaW81TTRLQXlDNGVEUHpaaHJmMWF4VGpKUDVqTkVZZmh3T2NnMG9GWE5ZZEZBaGNrSXlUYS1EQ2wwcG9lN0w5d2pOV0JWajJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOcnhQOThXU3hIaWsxVHdVdGdFdjA4eHVLODhoR3pVdTVUY0Z3MEhfYzBjWVNtbHFkLXB5M3FvR0dqclV3d2FCZzJVOHg3UmtNejBBS2ZhTllTaWlES09IRHdheUtVU0NjYWRZS19qV1V6SGVWbHhmUjRxd0hyOWR3OXh4a0lpamxaNlE?oc=5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="K29" s="1" t="n">
-        <v>46134.34027777778</v>
+        <v>46134.32136574074</v>
       </c>
     </row>
     <row r="30">
@@ -2030,22 +2030,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Barnet park double stabbing victims rushed to hospital as 'priority' - My London</t>
+          <t>Terrorist who planned to bomb London Stock Exchange was allowed to stay in UK - The Sun</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Barnet park double stabbing victims rushed to hospital as 'priority' - My London</t>
+          <t>Terrorist who planned to bomb London Stock Exchange was allowed to stay in UK - The Sun</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 10:29:00 GMT</t>
+          <t>Wed, 22 Apr 2026 08:10:00 GMT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMlFhMUE4LTNXOTdzQW5VZ0p5VDBrUnB6dlJaZWgzNzJkcUg0a3VUZndpV2lUMERIZF9vRGVoMXhNTFM4T3NyUHo2NWF6N2xoR3YzLTlYSmI1d3pyd2Q0ajZNMWxSNkpuY1lIZmc3ZmdKdERoeEFVazY4ek9nYXpwVkctai1wcC1JQ1JoRWxxVlphaGkwZjF6MtIBngFBVV95cUxQSGhNVTlmSHVkNmpoLThSX0pyenR3SGUteVF3ZW5VRWw0YVAwZU5tVGszYU5vclZQMXBJRDFQc3MyeWg5cWsyQmpOTUUtN1ZDNnZjcUdOM1lqMkd3bldJQUREbEhrUVZvVkoxZEtfZWFHb2I5RWI1Mm1zNlpjeWlqamtHY2gwTGxQdGNZdTJubHJSeEI1WmsxVzdZN2FKQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOZFlwT3NoaG5aZXY3a25VYlJIWGZ6VERlRVNZZHF4dmVLaEtQLXJLTVJtRF9ydHhSOVhEWlozeXUycWIyeHkwaW81TTRLQXlDNGVEUHpaaHJmMWF4VGpKUDVqTkVZZmh3T2NnMG9GWE5ZZEZBaGNrSXlUYS1EQ2wwcG9lN0w5d2pOV0JWajJ3?oc=5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="K30" s="1" t="n">
-        <v>46134.43680555555</v>
+        <v>46134.34027777778</v>
       </c>
     </row>
     <row r="31">
@@ -2080,27 +2080,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>UK inflation rises after Iran war pushes up fuel prices - BBC</t>
+          <t>Barnet park double stabbing victims rushed to hospital as 'priority' - My London</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>UK inflation rises after Iran war pushes up fuel prices - BBC</t>
+          <t>Barnet park double stabbing victims rushed to hospital as 'priority' - My London</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 08:38:11 GMT</t>
+          <t>Wed, 22 Apr 2026 10:29:00 GMT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9fWHdxUWgzM2ZzdG14Um5wdXFST3cySWF5c0pqX1ZpclNfUlF2YUlfdDZ4UDdmWHhyQkZmdGgtTzY4TVo2dS1UR1ZaandCOVJrOG9NVkluSFEtdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMlFhMUE4LTNXOTdzQW5VZ0p5VDBrUnB6dlJaZWgzNzJkcUg0a3VUZndpV2lUMERIZF9vRGVoMXhNTFM4T3NyUHo2NWF6N2xoR3YzLTlYSmI1d3pyd2Q0ajZNMWxSNkpuY1lIZmc3ZmdKdERoeEFVazY4ek9nYXpwVkctai1wcC1JQ1JoRWxxVlphaGkwZjF6MtIBngFBVV95cUxQSGhNVTlmSHVkNmpoLThSX0pyenR3SGUteVF3ZW5VRWw0YVAwZU5tVGszYU5vclZQMXBJRDFQc3MyeWg5cWsyQmpOTUUtN1ZDNnZjcUdOM1lqMkd3bldJQUREbEhrUVZvVkoxZEtfZWFHb2I5RWI1Mm1zNlpjeWlqamtHY2gwTGxQdGNZdTJubHJSeEI1WmsxVzdZN2FKQQ?oc=5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="K31" s="1" t="n">
-        <v>46134.35984953704</v>
+        <v>46134.43680555555</v>
       </c>
     </row>
     <row r="32">
@@ -2140,22 +2140,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Solidarity with London Met strike - socialistparty.org.uk</t>
+          <t>UK inflation rises after Iran war pushes up fuel prices - BBC</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Solidarity with London Met strike - socialistparty.org.uk</t>
+          <t>UK inflation rises after Iran war pushes up fuel prices - BBC</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 10:33:00 GMT</t>
+          <t>Wed, 22 Apr 2026 08:38:11 GMT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPYlQ3SU1uQ2FDaXE2aTBiM05MeExVZmEyYjZzeXQ5bUJxa2hjR0ZUekFuZnk5VW9sX0xXR1RNWlVXazNNdHFBVGc2bU5TdEZVTGlSXzRGNzhDbmRsNzNramt4RmUzYmJmaGVKZjAxZF9kcmtOdVNDSU5RcTV2UTl6SXJ3Z1AxNWRUVGtCLW9fZmpuNjZvcnJ2RTFGTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9fWHdxUWgzM2ZzdG14Um5wdXFST3cySWF5c0pqX1ZpclNfUlF2YUlfdDZ4UDdmWHhyQkZmdGgtTzY4TVo2dS1UR1ZaandCOVJrOG9NVkluSFEtdw?oc=5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="K32" s="1" t="n">
-        <v>46134.43958333333</v>
+        <v>46134.35984953704</v>
       </c>
     </row>
     <row r="33">
@@ -2195,22 +2195,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Full list of London Underground line closures as 24-hour strike ends - London Evening Standard</t>
+          <t>Solidarity with London Met strike - socialistparty.org.uk</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Full list of London Underground line closures as 24-hour strike ends - London Evening Standard</t>
+          <t>Solidarity with London Met strike - socialistparty.org.uk</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 11:39:12 GMT</t>
+          <t>Wed, 22 Apr 2026 10:33:00 GMT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQNFd1aFFZMm5SNHUxLVRQZG1UV3Y1WmFfcS01dUFqaXowa0RPRzF5U2ctNlUtNENPN1hRNFNxbnJpS1pCTERRMm9IRTRFRjdMbnppOUU2Vlh3ekFjN2pDZzNWVGItOTc3NXQxU20tNzV1dE0wa01yWHdvbUtFRkY1c2xQRFdNMFl4WUhYSE4wZ1kyMUY2LVgzbUFYbjZGWFNyZzJmOEdDdmxnQzQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPYlQ3SU1uQ2FDaXE2aTBiM05MeExVZmEyYjZzeXQ5bUJxa2hjR0ZUekFuZnk5VW9sX0xXR1RNWlVXazNNdHFBVGc2bU5TdEZVTGlSXzRGNzhDbmRsNzNramt4RmUzYmJmaGVKZjAxZF9kcmtOdVNDSU5RcTV2UTl6SXJ3Z1AxNWRUVGtCLW9fZmpuNjZvcnJ2RTFGTQ?oc=5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="K33" s="1" t="n">
-        <v>46134.48555555556</v>
+        <v>46134.43958333333</v>
       </c>
     </row>
     <row r="34">
@@ -2250,22 +2250,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>When does the Tube strike end today? How long London Underground walkout lasts and why it's happening - The Sun</t>
+          <t>Full list of London Underground line closures as 24-hour strike ends - London Evening Standard</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>When does the Tube strike end today? How long London Underground walkout lasts and why it's happening - The Sun</t>
+          <t>Full list of London Underground line closures as 24-hour strike ends - London Evening Standard</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 08:29:50 GMT</t>
+          <t>Wed, 22 Apr 2026 11:39:12 GMT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQdHN6VjFtX0hld25BMWRHODlaSHptcXd4dXhTZEFlWmd2cmViVWZxdWhYUDNwanZEUWZRTlFLYkRIVWZweXlSemtaX1ZLcEktN0MxYm9tNkZFaWtOektQOHZWQld1dGxEUEYtYXFER01QMGlZeWxtbTVMU3B1YkY1eFE1OGwtX1JWcExiRld2Qnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQNFd1aFFZMm5SNHUxLVRQZG1UV3Y1WmFfcS01dUFqaXowa0RPRzF5U2ctNlUtNENPN1hRNFNxbnJpS1pCTERRMm9IRTRFRjdMbnppOUU2Vlh3ekFjN2pDZzNWVGItOTc3NXQxU20tNzV1dE0wa01yWHdvbUtFRkY1c2xQRFdNMFl4WUhYSE4wZ1kyMUY2LVgzbUFYbjZGWFNyZzJmOEdDdmxnQzQ?oc=5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2289,7 +2289,7 @@
         </is>
       </c>
       <c r="K34" s="1" t="n">
-        <v>46134.35405092593</v>
+        <v>46134.48555555556</v>
       </c>
     </row>
     <row r="35">
@@ -2305,22 +2305,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Higher energy prices drive UK consumer prices up in March - Anadolu Ajansı</t>
+          <t>When does the Tube strike end today? How long London Underground walkout lasts and why it's happening - The Sun</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Higher energy prices drive UK consumer prices up in March - Anadolu Ajansı</t>
+          <t>When does the Tube strike end today? How long London Underground walkout lasts and why it's happening - The Sun</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 08:51:12 GMT</t>
+          <t>Wed, 22 Apr 2026 08:29:50 GMT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOYkRYTm42YU5PWVRjbDMtUDQtcnhianhkYWNBb0pDRFVJdW9DbDNFV2dnZEx5bjVQNzZfMjNkU2NDZGdQV2lMblE5azJvSmlDT1kxWVVwQU9GS0M5SzRFVDhJcURtcC1BMXRrTkR0ZUs2bEJWc1pjT21zNE9DWGR6M2loeUpTbzgzZU1GYnZDVV9TcDFESVQ0LWs1bVBqLUk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQdHN6VjFtX0hld25BMWRHODlaSHptcXd4dXhTZEFlWmd2cmViVWZxdWhYUDNwanZEUWZRTlFLYkRIVWZweXlSemtaX1ZLcEktN0MxYm9tNkZFaWtOektQOHZWQld1dGxEUEYtYXFER01QMGlZeWxtbTVMU3B1YkY1eFE1OGwtX1JWcExiRld2Qnc?oc=5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="K35" s="1" t="n">
-        <v>46134.36888888889</v>
+        <v>46134.35405092593</v>
       </c>
     </row>
     <row r="36">
@@ -2360,22 +2360,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>London Underground Strike: Understanding the Current Disruptions - DM News</t>
+          <t>Higher energy prices drive UK consumer prices up in March - Anadolu Ajansı</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>London Underground Strike: Understanding the Current Disruptions - DM News</t>
+          <t>Higher energy prices drive UK consumer prices up in March - Anadolu Ajansı</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 09:09:21 GMT</t>
+          <t>Wed, 22 Apr 2026 08:51:12 GMT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNbXFOOFRCUzVCNzZoMEY5eUpzRFJSMG9YdDhDYnFFeHdCeFBiQVRrVzBWcDRyMzNSX1l6WW10UVVOdWR1b2xieXhvSW5pNFZxam9WVFBfWEZDTk5WWDN3b2M1VlZGVi1nV0wxRWFvSlNZTFZRMndDREdTenlRdkZNMlJsWEQ1aVEtT0F3V0pB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOYkRYTm42YU5PWVRjbDMtUDQtcnhianhkYWNBb0pDRFVJdW9DbDNFV2dnZEx5bjVQNzZfMjNkU2NDZGdQV2lMblE5azJvSmlDT1kxWVVwQU9GS0M5SzRFVDhJcURtcC1BMXRrTkR0ZUs2bEJWc1pjT21zNE9DWGR6M2loeUpTbzgzZU1GYnZDVV9TcDFESVQ0LWs1bVBqLUk?oc=5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2399,38 +2399,38 @@
         </is>
       </c>
       <c r="K36" s="1" t="n">
-        <v>46134.38149305555</v>
+        <v>46134.36888888889</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>High Level City Italy Italian</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>In arrivo uno sciopero Atm a Milano: gli orari di metro, bus e tram (e le fasce di garanzia) - MilanoToday</t>
+          <t>London Underground Strike: Understanding the Current Disruptions - DM News</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>An ATM strike is coming to Milan: metro, bus and tram timetables (and guarantee periods) - MilanoToday</t>
+          <t>London Underground Strike: Understanding the Current Disruptions - DM News</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 07:30:25 GMT</t>
+          <t>Wed, 22 Apr 2026 09:09:21 GMT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOR183OEFPOERIUUd4RGF3bjFWNVZ4bF9ZWmVhSy1QT1ZwaFliT3N5MFpqaHJGNzBHdGdGWkJlNzJSZUtpeWUwWGlqNGFlXzB5UEhqNXRQZXhWVHM3U2VPejg5TzliY2djV2ZGM2JUYWVNVFFiT3BnWlEwVHhjdVBPZFZoUGlZOVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNbXFOOFRCUzVCNzZoMEY5eUpzRFJSMG9YdDhDYnFFeHdCeFBiQVRrVzBWcDRyMzNSX1l6WW10UVVOdWR1b2xieXhvSW5pNFZxam9WVFBfWEZDTk5WWDN3b2M1VlZGVi1nV0wxRWFvSlNZTFZRMndDREdTenlRdkZNMlJsWEQ1aVEtT0F3V0pB?oc=5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2440,52 +2440,52 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>IT:it</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K37" s="1" t="n">
-        <v>46134.31278935185</v>
+        <v>46134.38149305555</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>High Level City Italy Italian</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cresce la protesta contro la strada trasformata in «parco giochi» - Milano Città Stato</t>
+          <t>Thousands of London commuters walk to work in underground strike - The Straits Times</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>The protest against the street transformed into a "playground" is growing - Milan City State</t>
+          <t>Thousands of London commuters walk to work in underground strike - The Straits Times</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 08:57:34 GMT</t>
+          <t>Wed, 22 Apr 2026 10:55:00 GMT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNWkx5Ry1JODhmZEp1WnlLLXJZcWNOclFHRWZmRGdxUXZBQ1Bac3k3QkVQVUViYWlpRWlITEd4NGZkSS15Y2NHdHhtaE41OTZTaTRrS3gtWGNXZTBVSkRtNnpIcWNhUGtlU29uWEN6X3d1ZFJqa1NlQXRicjNxSEgyUlR4N2hLallWMW8tSDljV1pfOVhUTXFRTkVraVo0dFdjV3RN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQN2JtcHRfZm9PTlphdmhuOVJUd0w3QTNzZ3BBZkhGVlNISENiWlUzYjhlb0I5NEFsTS0wb0RwYUxPaFVxSXZRV0FXd2tEMzRsZlVOZ3NQMHJwRU5vdEd2X1ZuMzRhdnVQaTFJZGprT05Dc091cVl5ZDNHbkc3S29jeUNqTUVmNXBWQmJSQURwUkwxOFlSTG1tM1ZwSUl1R0c0MjFBdmxmLS1wZw?oc=5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2495,21 +2495,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>IT:it</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K38" s="1" t="n">
-        <v>46134.37331018518</v>
+        <v>46134.45486111111</v>
       </c>
     </row>
     <row r="39">
@@ -2525,22 +2525,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Borsa italiana – Euronext: governance in crisi, lavoratori marginalizzati. il 30 aprile sciopero nazionale - firstcisl.it</t>
+          <t>In arrivo uno sciopero Atm a Milano: gli orari di metro, bus e tram (e le fasce di garanzia) - MilanoToday</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Italian stock exchange – Euronext: governance in crisis, marginalized workers. national strike on April 30th - firstcisl.it</t>
+          <t>An ATM strike is coming to Milan: metro, bus and tram timetables (and guarantee periods) - MilanoToday</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 10:45:32 GMT</t>
+          <t>Wed, 22 Apr 2026 07:30:25 GMT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQdHl5bkNXajRDLWJlNHRZaF95N3dBb2d6aUpmWmJyZWRPVlllLUlaMG9vbnFNSFVGOFB4d01kZExQUVNTallrRjMzOEpldmNkY0xLNVpjN3VscjNtYlNWa1o4emxLMTFMaUpJbGV3d1hueWhlTUU2blN1ODltMWMxelRXQ2Z2THBjTV9SLTdkM1JQRmRtdld4SEpIRnAtS09PdFhzc2ZuSGg0RjdGMzYxemEtU0N2TzViME9NZDNaaC04bUtxc0tHcENDcVVyVVZvYWRKd3VuVXhoQnhvb1hTX241WDlOaXZ3OHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOR183OEFPOERIUUd4RGF3bjFWNVZ4bF9ZWmVhSy1QT1ZwaFliT3N5MFpqaHJGNzBHdGdGWkJlNzJSZUtpeWUwWGlqNGFlXzB5UEhqNXRQZXhWVHM3U2VPejg5TzliY2djV2ZGM2JUYWVNVFFiT3BnWlEwVHhjdVBPZFZoUGlZOVk?oc=5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2564,7 +2564,7 @@
         </is>
       </c>
       <c r="K39" s="1" t="n">
-        <v>46134.44828703703</v>
+        <v>46134.31278935185</v>
       </c>
     </row>
     <row r="40">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bologna, l'accoglienza diventa casa in una rete di speranza della comunità di Villaregia - Vatican News</t>
+          <t>Cresce la protesta contro la strada trasformata in «parco giochi» - Milano Città Stato</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Bologna, hospitality becomes home in a network of hope of the Villaregia community - Vatican News</t>
+          <t>The protest against the street transformed into a "playground" is growing - Milan City State</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 12:14:49 GMT</t>
+          <t>Wed, 22 Apr 2026 08:57:34 GMT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOUWxCak04bE03VnNZaWtoWXR5Snd5YXMyUHRRSm9TY1E1VG5VN0JfNk12TUNpU2NVWGpSeDRqUWdyUHFudTBwTHVJa2RWMjJaeGozTkNhXzNiNVgwLVA3MFlVSXVzR3JLNHctenZwWlpLV1FBVVFnM05UcFNjVlJiTGNMdjNEUENMNTVuRldmODl4OHF5UE1yeGozLU8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNWkx5Ry1JODhmZEp1WnlLLXJZcWNOclFHRWZmRGdxUXZBQ1Bac3k3QkVQVUViYWlpRWlITEd4NGZkSS15Y2NHdHhtaE41OTZTaTRrS3gtWGNXZTBVSkRtNnpIcWNhUGtlU29uWEN6X3d1ZFJqa1NlQXRicjNxSEgyUlR4N2hLallWMW8tSDljV1pfOVhUTXFRTkVraVo0dFdjV3RN?oc=5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="K40" s="1" t="n">
-        <v>46134.51028935185</v>
+        <v>46134.37331018518</v>
       </c>
     </row>
     <row r="41">
@@ -2635,45 +2635,155 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>Borsa italiana – Euronext: governance in crisi, lavoratori marginalizzati. il 30 aprile sciopero nazionale - firstcisl.it</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Italian stock exchange – Euronext: governance in crisis, marginalized workers. national strike on April 30th - firstcisl.it</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Wed, 22 Apr 2026 10:45:32 GMT</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQdHl5bkNXajRDLWJlNHRZaF95N3dBb2d6aUpmWmJyZWRPVlllLUlaMG9vbnFNSFVGOFB4d01kZExQUVNTallrRjMzOEpldmNkY0xLNVpjN3VscjNtYlNWa1o4emxLMTFMaUpJbGV3d1hueWhlTUU2blN1ODltMWMxelRXQ2Z2THBjTV9SLTdkM1JQRmRtdld4SEpIRnAtS09PdFhzc2ZuSGg0RjdGMzYxemEtU0N2TzViME9NZDNaaC04bUtxc0tHcENDcVVyVVZvYWRKd3VuVXhoQnhvb1hTX241WDlOaXZ3OHc?oc=5</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K41" s="1" t="n">
+        <v>46134.44828703703</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>High Level City Italy Italian</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Bologna, l'accoglienza diventa casa in una rete di speranza della comunità di Villaregia - Vatican News</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Bologna, hospitality becomes home in a network of hope of the Villaregia community - Vatican News</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Wed, 22 Apr 2026 12:14:49 GMT</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOUWxCak04bE03VnNZaWtoWXR5Snd5YXMyUHRRSm9TY1E1VG5VN0JfNk12TUNpU2NVWGpSeDRqUWdyUHFudTBwTHVJa2RWMjJaeGozTkNhXzNiNVgwLVA3MFlVSXVzR3JLNHctenZwWlpLV1FBVVFnM05UcFNjVlJiTGNMdjNEUENMNTVuRldmODl4OHF5UE1yeGozLU8?oc=5</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K42" s="1" t="n">
+        <v>46134.51028935185</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>High Level City Italy Italian</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>Cappello Alpino a 180 volontari delle Olimpiadi, monta la protesta e c'è chi lascia l'Ana. La lettera di un 'vecio': "Superato un punto non più oltrepassabile" - il Dolomiti</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>Alpine hats to 180 Olympic volunteers, the protest mounts and some leave the ANA. The letter from an 'old man': "Passed a point that can no longer be crossed" - the Dolomites</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 10:28:14 GMT</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMimAJBVV95cUxPZlM3c0UtTjNydVoxQjF1VzJZS2ZIVkEwdnpjQmxhTjhlYTRXeTgxRDU2LUNkLWJ1N0xSZzZocXZrekZnbkhUdlZpOU9iWVM0eUl2bEs1akFPS21EbGxpQTZUOU5lT3NvaElVUU1KaE5pN2VKVGRNU3hkODhfWTJYOWNsVjFQVHhZS3BWQlZhLXBFUWJZdG9GNlhycmxkYXFNQkgwVDUtbHNqeTFtSWpwTFE1Y01ld0NEM0h2T0tRYzBXYUlwZFVUVEo1ZUJSb182eUEybXVLellCQXVlNXk3Q0g1OEl6SGlYakE4cXY0T0hRcDlLUkxDZ09qTjJZMlFpRkdWWFQ2Zlc0M05SVjV2dDhORzJSRXFv?oc=5</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
         <is>
           <t>it</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>IT:it</t>
         </is>
       </c>
-      <c r="K41" s="1" t="n">
+      <c r="K43" s="1" t="n">
         <v>46134.43627314815</v>
       </c>
     </row>
